--- a/sources/forest_step7.xlsx
+++ b/sources/forest_step7.xlsx
@@ -417,14 +417,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA121"/>
+  <dimension ref="A1:AB121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -443,10 +443,11 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="113" customWidth="1" min="23" max="23"/>
-    <col width="38" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="38" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="38" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,20 +575,25 @@
       </c>
       <c r="X2" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -649,12 +655,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>eb75d0d7-52ff-4314-bc16-0e3a2de06ca5</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>86ce092a-ed1b-4488-8b43-83bb797e1953</t>
         </is>
@@ -716,12 +722,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>2742d290-896d-4e67-bcf2-eadd0f342937</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>208902ee-c1ea-4722-b43f-498cc20ea479</t>
         </is>
@@ -783,12 +789,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>2b6913a6-c3a8-4044-ab16-7722f089e15d</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>3629c8e0-f9d4-46c6-a822-fa70ee4964df</t>
         </is>
@@ -797,22 +803,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>f,f+3+4 [~5]</t>
+          <t>f,f+3+4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>f,f+3+4 [~5]</t>
+          <t>f,f+3+4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Dragon Knee [Tag]</t>
+          <t>Dragon Knee</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dragon Knee [Tag]</t>
+          <t>Dragon Knee</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -852,10 +858,15 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>33c118ea-0ce9-4ac8-aae0-7e8cfb8ee10f</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>e5a6f6a2-c7c3-4a91-ada3-76198bb6afe4</t>
         </is>
@@ -917,12 +928,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>8598ba4a-c4d7-4e2c-83dc-cab315994e9b</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>47921123-a4d5-4452-85fc-97f92e413bbd</t>
         </is>
@@ -979,17 +990,17 @@
           <t>The initial grab does no damage.</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>c496aa41-bc15-473a-b020-7fdb437577cf</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>3629c8e0-f9d4-46c6-a822-fa70ee4964df</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1046,12 +1057,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>daf033ef-4b67-4b29-86af-e6b2fab70477</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1108,12 +1119,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>1726e35f-9e18-4c65-a787-332f9f98cc84</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1170,12 +1181,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>a1c6311d-6e89-4a3a-b759-44f0ce100eea</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1307,20 +1318,25 @@
       </c>
       <c r="X14" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y14" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y14" s="1" t="inlineStr">
+      <c r="Z14" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z14" s="1" t="inlineStr">
+      <c r="AA14" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA14" s="1" t="inlineStr">
+      <c r="AB14" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1402,12 +1418,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>846fcc6d-3111-4c5d-a4c4-a362c8c14874</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>ecdfa790-fe69-4945-ae9e-2d1ccdd25e6a</t>
         </is>
@@ -1489,12 +1505,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>98452a63-d79d-4b94-9ff8-4b8a12da4fc8</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>5ada3d3a-4405-484e-955f-144e5b6cb08a</t>
         </is>
@@ -1576,12 +1592,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>692fa728-69cc-4c77-8b02-69f90748928b</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>85de8566-634f-47c3-a81d-5ff6461658d5</t>
         </is>
@@ -1663,12 +1679,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>c70364cc-05f8-4fbf-9408-46a803db54f7</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>8e17b408-b912-473a-bab6-95f13786c8fe</t>
         </is>
@@ -1750,12 +1766,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>1ea6009a-8f7a-438f-a2b9-4d1baf4a76d7</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>094615ec-a403-4b09-b8d6-2a9870ee9500</t>
         </is>
@@ -1837,12 +1853,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>0b40bed6-0300-4d49-a194-d6e681de5cbb</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>7cd9d042-8301-413b-84b8-0f3c8e8b4d28</t>
         </is>
@@ -1924,12 +1940,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>d08371b3-e8be-4228-ab0c-bc0e18dbd9c5</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>a5832153-a6e9-48f2-ab94-f9740fd88cc0</t>
         </is>
@@ -2011,12 +2027,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>95d6f842-81dc-4ab1-aaba-3192b332bb65</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>1ffce1a0-58a4-4936-94e5-362ae85b592a</t>
         </is>
@@ -2098,12 +2114,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>ba8e326d-561b-467c-a36e-52663905707f</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>eb2e5e30-bf32-4471-8aab-aaa80ab82173</t>
         </is>
@@ -2185,12 +2201,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>ebd7329c-2813-4975-9229-9d4645409eb3</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>417d1249-69bf-42e4-9fbd-2c9b600d25f2</t>
         </is>
@@ -2272,12 +2288,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>865fdbdc-9505-4f68-9fb5-89ca557bc10a</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>19e89ffd-4511-47c3-9fb6-1fa914fc2e0b</t>
         </is>
@@ -2359,12 +2375,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>46d9a77d-c02d-4b29-ab15-7a4c0918617d</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>3793287f-d150-4d4b-bbe2-a3c3830d3f00</t>
         </is>
@@ -2446,12 +2462,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>3d1b19ee-49e9-4c47-977d-a91662df58dd</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>830467d7-42b5-48fe-a00b-9ec559f7fd6d</t>
         </is>
@@ -2533,12 +2549,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>dcf070b2-475d-4b5f-a3a8-6e150a705193</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>8487f336-b04d-4722-a47f-453929d43893</t>
         </is>
@@ -2620,12 +2636,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>ec63bc40-06c9-4cbb-8e50-a59621af3a3c</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>a090d6cc-c4f7-42df-9edc-ad2dc3e8bb0e</t>
         </is>
@@ -2707,12 +2723,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>8010d3e2-601a-4451-8730-b34b77cce8ad</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>151f630d-b78f-4abb-9497-5f279cabf432</t>
         </is>
@@ -2794,12 +2810,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>db1ac351-dccd-40ca-9982-ec5e92c2472d</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>1c96bc36-db75-4e7c-a980-0c28d1ee821b</t>
         </is>
@@ -2881,12 +2897,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>b784f223-b8d7-4998-afc9-43a73aefc35f</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>3b106da2-c840-426c-bc80-990302faf56b</t>
         </is>
@@ -2968,12 +2984,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>950111d8-a1cb-4043-8bd2-07c00ffed25e</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>a943b002-3e0a-4501-8626-078a5ce0fd03</t>
         </is>
@@ -3055,12 +3071,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>6ada5491-5c04-4c71-b753-7f6473677e8f</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>bfead083-cfda-401f-9195-27d27aece5ef</t>
         </is>
@@ -3142,12 +3158,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>be7055c9-78c7-463c-9a9d-b809e6aa3bc3</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>ffc87ae5-e6a7-46cc-b4c6-807cb76e0f00</t>
         </is>
@@ -3229,12 +3245,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>5a299059-c1ea-49e2-9894-40ffd27848f6</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>990139ff-b876-41eb-b8dc-5f34b2236522</t>
         </is>
@@ -3316,12 +3332,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>e4e006f1-9086-4d8f-a4d6-e699fa157944</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>78f3787c-e9c4-44cd-bc08-4c05effa7fd2</t>
         </is>
@@ -3403,12 +3419,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>706c1355-0eef-426b-b7a4-930208fb125c</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>b4205a4a-bd91-4007-a9a9-c477bdef7169</t>
         </is>
@@ -3540,20 +3556,25 @@
       </c>
       <c r="X41" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y41" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y41" s="1" t="inlineStr">
+      <c r="Z41" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z41" s="1" t="inlineStr">
+      <c r="AA41" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA41" s="1" t="inlineStr">
+      <c r="AB41" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3645,12 +3666,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>b1fad16c-d1ab-43bf-91ca-f87a587f8a4c</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>7b322a83-a687-43cb-bd98-d3e27d5223b6</t>
         </is>
@@ -3742,12 +3763,12 @@
           <t>hhhhh</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>7894ce56-f888-482e-8346-c6b7cce7de27</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>a57dabb6-18c8-4d8b-b8fa-e8de7ad3a55a</t>
         </is>
@@ -3839,17 +3860,17 @@
           <t>Link after the 1st, 2nd, 3rd or 4th hit of the Machine Gun Arrow.</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>5cd4b3ec-d078-43e5-9fa3-46fea41735c6</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>2e3bf969-c77a-4630-b766-130ccd488c19</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>7894ce56-f888-482e-8346-c6b7cce7de27</t>
         </is>
@@ -3941,17 +3962,17 @@
           <t>Link after the 1st, 2nd, 3rd or 4th hit of the Machine Gun Arrow.</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>a30a5d44-0fe7-4c2f-b4b0-efcadc97d18a</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>292c9d0a-37d4-4ab2-b37c-3d87473c1825</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>7894ce56-f888-482e-8346-c6b7cce7de27</t>
         </is>
@@ -4048,12 +4069,12 @@
           <t>KNDc</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>91803a14-fec7-4773-b62b-13521abe9dba</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>6893956d-1d83-4bd3-936a-84f293de0d97</t>
         </is>
@@ -4125,17 +4146,17 @@
           <t>hhhh</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>d8cdd46e-bf64-4691-83d1-9484fd54d55d</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>82ef7d70-299a-4074-ae3d-4ae24589bb12</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>91803a14-fec7-4773-b62b-13521abe9dba</t>
         </is>
@@ -4207,17 +4228,17 @@
           <t>hhm</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>56ac1113-59f7-4035-bacb-1cfb93409c2f</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>09dfb2f9-d2a5-4c4a-8072-2ba875b94509</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>91803a14-fec7-4773-b62b-13521abe9dba</t>
         </is>
@@ -4226,22 +4247,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>b+1&lt;2&lt;1 [~5]</t>
+          <t>b+1&lt;2&lt;1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>b+1&lt;2&lt;1 [~5]</t>
+          <t>b+1&lt;2&lt;1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Dragon Storm [Tag]</t>
+          <t>Dragon Storm</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dragon Storm [Tag]</t>
+          <t>Dragon Storm</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4316,10 +4337,15 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
           <t>47f4c7a5-7c8a-438d-a627-fe64ea1bff20</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>3ea8dce0-2cc4-41e4-aa7f-8587c8da38fd</t>
         </is>
@@ -4421,12 +4447,12 @@
           <t>OB</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>7eca98c0-bb23-47de-8c5f-11abe6ffcdda</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>dba4575a-cfbf-434b-8f0e-8ae3fd0b8ce2</t>
         </is>
@@ -4523,12 +4549,12 @@
           <t>GB BNc</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>9307051c-b715-442d-ba29-272853595ec5</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>d98cc2c0-e72b-42f5-b345-c2dfc9753ebb</t>
         </is>
@@ -4620,12 +4646,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>c4740abf-f183-4099-8d0d-b6e405947998</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>582df07f-40e2-453b-94f1-30e70869c3ba</t>
         </is>
@@ -4717,12 +4743,12 @@
           <t>hmh</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>3d6c9e59-eff8-4bc3-b25e-472075c08542</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>5c2138bc-6b47-4a5c-9ccb-553131c1231f</t>
         </is>
@@ -4731,22 +4757,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>f+2~1 [~5]</t>
+          <t>f+2~1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>f+2~1 [~5]</t>
+          <t>f+2~1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Poison Arrow [Tag]</t>
+          <t>Poison Arrow</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Poison Arrow [Tag]</t>
+          <t>Poison Arrow</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4826,10 +4852,15 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
           <t>3aeae3d1-c6da-4a85-917d-2714becb2ac9</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>b3af83f8-dd54-4571-bbcd-e7c58a2cef35</t>
         </is>
@@ -4921,12 +4952,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>b79714f1-cdec-4348-a27c-fed0d43c4d84</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>7030bac0-d1cb-48d7-9a47-b6882451df04</t>
         </is>
@@ -5013,17 +5044,17 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>11cd67de-7112-4c05-acef-561f7c109875</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>b7432cce-51c3-4ce0-bdec-48c3d32028d9</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>b79714f1-cdec-4348-a27c-fed0d43c4d84</t>
         </is>
@@ -5032,22 +5063,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>b+2,3,4 [~5]</t>
+          <t>b+2,3,4</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>b+2,3,4 [~5]</t>
+          <t>b+2,3,4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Junkyard Combo [Tag]</t>
+          <t>Junkyard Combo</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Junkyard Combo [Tag]</t>
+          <t>Junkyard Combo</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5122,10 +5153,15 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
           <t>b6d11ba5-d212-47a4-a893-508b9c1a81c7</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>85a95822-6877-45cc-bf73-1c9b8713900f</t>
         </is>
@@ -5222,12 +5258,12 @@
           <t>sm</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>d4907eb7-4cf4-400c-b6fc-9413e19273d5</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>bb86d158-8a65-4a3e-a4c7-ec1149ee74ac</t>
         </is>
@@ -5236,22 +5272,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>WS+2 [~5]</t>
+          <t>WS+2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WS+2 [~5]</t>
+          <t>WS+2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Dragon Upper [Tag]</t>
+          <t>Dragon Upper</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dragon Upper [Tag]</t>
+          <t>Dragon Upper</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5326,10 +5362,15 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
           <t>e5961f74-a371-4667-a7d7-de2eca4f72b7</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>e54862d7-358a-4d91-b16d-3be49e1c70f5</t>
         </is>
@@ -5426,12 +5467,12 @@
           <t>First hit is 5 damage if the second hit is not executed.</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>4a5a8aa6-2f43-4cab-a742-fc10aa810a34</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>70055806-dc83-43b4-a6b6-228a6e0239d1</t>
         </is>
@@ -5440,22 +5481,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3&lt;4 [~5]</t>
+          <t>3&lt;4</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3&lt;4 [~5]</t>
+          <t>3&lt;4</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Head Kick - Somersault - [Tag]</t>
+          <t>Head Kick - Somersault -</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Head Kick - Somersault - [Tag]</t>
+          <t>Head Kick - Somersault -</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5530,10 +5571,15 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
           <t>4924ea9b-ac92-4461-a03b-f1759461f9c9</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>fdbeaaad-53ea-4bd6-b1ae-2203a39233d3</t>
         </is>
@@ -5542,22 +5588,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3,3,4 [~5]</t>
+          <t>3,3,4</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3,3,4 [~5]</t>
+          <t>3,3,4</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Double Kick - Somersault [Tag]</t>
+          <t>Double Kick - Somersault</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Double Kick - Somersault [Tag]</t>
+          <t>Double Kick - Somersault</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5632,10 +5678,15 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
           <t>90be7a3e-bd7d-4357-80e1-81af675a249d</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>d7d512fc-c66d-470b-82b5-598d9d922d6a</t>
         </is>
@@ -5727,12 +5778,12 @@
           <t>hhm</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>f0f19abc-7f51-4257-bc70-1fc9f9edd818</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>0ce470dd-43c2-4611-9565-0c9d6689b048</t>
         </is>
@@ -5741,22 +5792,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3,3,3,4 [~5]</t>
+          <t>3,3,3,4</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>3,3,3,4 [~5]</t>
+          <t>3,3,3,4</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Triple Kick - Roundhouse [Tag]</t>
+          <t>Triple Kick - Roundhouse</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Triple Kick - Roundhouse [Tag]</t>
+          <t>Triple Kick - Roundhouse</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5836,10 +5887,15 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
           <t>0a950c73-457c-4b22-b52f-70e8216260dd</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>0c50e3d5-699f-4fb2-9d45-3382cba9b132</t>
         </is>
@@ -5931,12 +5987,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>e0a8a153-4505-428d-87fc-638ac10b43d5</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>07c86591-4324-478a-af8a-d32405a3ec16</t>
         </is>
@@ -6028,12 +6084,12 @@
           <t>mlh</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>60f2d718-a980-4133-92be-35ebb103b060</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>407bca1d-0719-409e-87ad-84329504a0d3</t>
         </is>
@@ -6125,12 +6181,12 @@
           <t>lh</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>27c94564-5bf6-4bc0-9bfc-2f34c03f918b</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>d2428f32-722f-46b3-8d3b-ae2da2067416</t>
         </is>
@@ -6217,17 +6273,17 @@
           <t>lhm</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>d795ef95-2961-45de-8d93-658aa67873c1</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>29e2d48c-f2ae-42ec-9942-a342f76fd07a</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>27c94564-5bf6-4bc0-9bfc-2f34c03f918b</t>
         </is>
@@ -6319,17 +6375,17 @@
           <t>JG RC</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>36990c24-6340-41e0-a016-68b978ba5f33</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>4880e7e4-8080-4666-8be6-c3d9130fa7d2</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>27c94564-5bf6-4bc0-9bfc-2f34c03f918b</t>
         </is>
@@ -6338,22 +6394,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>– 3,4 [~5]</t>
+          <t>– 3,4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>d+3,3,3,4 [~5]</t>
+          <t>d+3,3,3,4</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>– Head Kick - Somersault [Tag]</t>
+          <t>– Head Kick - Somersault</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rave Kicks – Head Kick - Somersault [Tag]</t>
+          <t>Rave Kicks – Head Kick - Somersault</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6423,15 +6479,20 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
           <t>e736318f-0524-488f-ab6b-acfbf5015b5d</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>1e7defdd-d028-4cf8-a27a-6c34599771ac</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>27c94564-5bf6-4bc0-9bfc-2f34c03f918b</t>
         </is>
@@ -6440,22 +6501,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>– 3,3,4 [~5]</t>
+          <t>– 3,3,4</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>d+3,3,3,3,4 [~5]</t>
+          <t>d+3,3,3,3,4</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>– Double Kick - Somersault [Tag]</t>
+          <t>– Double Kick - Somersault</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rave Kicks – Double Kick - Somersault [Tag]</t>
+          <t>Rave Kicks – Double Kick - Somersault</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6530,15 +6591,20 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
           <t>6976372b-41df-4861-acfe-8e91cbc311e1</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>68e815de-3c84-4137-9a13-b50a573fded2</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>27c94564-5bf6-4bc0-9bfc-2f34c03f918b</t>
         </is>
@@ -6625,17 +6691,17 @@
           <t>lhhm</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>18f5d67a-b59c-4eb6-9811-bb4fbab2fe80</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>05fd632d-2c18-4ca6-a1a5-21c0fccf23ce</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>27c94564-5bf6-4bc0-9bfc-2f34c03f918b</t>
         </is>
@@ -6737,12 +6803,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>103b9e98-8401-4280-8c54-718ad827f5e2</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>3f5d6199-f9a4-4cf5-8692-b173164a3ee6</t>
         </is>
@@ -6824,12 +6890,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="Y74" t="inlineStr">
         <is>
           <t>460e5fa0-89ed-4c35-95a4-0140412032e5</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>ce776ced-632a-4295-91ac-e6afe4f709ee</t>
         </is>
@@ -6838,22 +6904,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FC+3,4 [~5]</t>
+          <t>FC+3,4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FC+3,4 [~5]</t>
+          <t>FC+3,4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Crouch Kick - Somersault [Tag]</t>
+          <t>Crouch Kick - Somersault</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Crouch Kick - Somersault [Tag]</t>
+          <t>Crouch Kick - Somersault</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6928,10 +6994,15 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
           <t>ca17bc29-62e2-451d-b5bf-61bdfd9194f5</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>db7428f5-4cd3-4fd2-8049-57d1fa95da5b</t>
         </is>
@@ -6940,22 +7011,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>WS+3,4 [~5]</t>
+          <t>WS+3,4</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WS+3,4 [~5]</t>
+          <t>WS+3,4</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Twist Kick - Somersault [Tag]</t>
+          <t>Twist Kick - Somersault</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Twist Kick - Somersault [Tag]</t>
+          <t>Twist Kick - Somersault</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -7035,10 +7106,15 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
           <t>9d933f6b-817a-40a7-a0db-747fda8dc0d5</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>e9e35296-7a6e-4f75-b0bc-efedd70d9e0a</t>
         </is>
@@ -7047,27 +7123,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ub+3,4 [~5]</t>
+          <t>ub+3,4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ub+3,4 [~5]</t>
+          <t>ub+3,4</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>u+3,4 [~5]; uf+3,4 [~5]</t>
+          <t>u+3,4; uf+3,4</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Jump Kick - Somersault [Tag]</t>
+          <t>Jump Kick - Somersault</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jump Kick - Somersault [Tag]</t>
+          <t>Jump Kick - Somersault</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -7147,10 +7223,15 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
           <t>cf83377b-0364-423b-9698-cf3346ec7dca</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>f43c6907-1913-42c1-be70-e4aca27d5c09</t>
         </is>
@@ -7242,12 +7323,12 @@
           <t>mh</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="Y78" t="inlineStr">
         <is>
           <t>ea45046f-f02e-48e2-bced-0227e681bb61</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>f2b8790f-1fe6-420e-8781-ff5047f5eeea</t>
         </is>
@@ -7339,12 +7420,12 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="Y79" t="inlineStr">
         <is>
           <t>751f0015-8ef6-45a1-93b9-a98433ce1588</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>ddd8454c-877a-441c-9d2b-d12f32a5e6f7</t>
         </is>
@@ -7353,22 +7434,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3+4 [~5]</t>
+          <t>3+4</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>3+4 [~5]</t>
+          <t>3+4</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Catapult Kick [Tag]</t>
+          <t>Catapult Kick</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Catapult Kick [Tag]</t>
+          <t>Catapult Kick</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -7443,10 +7524,15 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
           <t>62bd6ad1-4839-408e-90e2-be9e8dd93ebd</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>066a0d31-5034-4795-9fa8-d477306e6a3a</t>
         </is>
@@ -7460,7 +7546,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>3+4 [~5],3</t>
+          <t>3+4,3</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7470,7 +7556,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Catapult Kick [Tag] – Twin Catapult</t>
+          <t>Catapult Kick – Twin Catapult</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7543,17 +7629,17 @@
           <t>Somersault will juggle on a hit if the previous kicks were blocked or whiffed.</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>b016ecd3-0a86-41a2-9980-d1a929f89109</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>132cb1f2-9772-4a50-b969-c9bfa631afba</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>62bd6ad1-4839-408e-90e2-be9e8dd93ebd</t>
         </is>
@@ -7645,12 +7731,12 @@
           <t>hhh</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="Y82" t="inlineStr">
         <is>
           <t>aeebee4a-2bb8-47e5-af49-f567114d9679</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>363d5918-81e3-484b-9a7f-328de221c708</t>
         </is>
@@ -7659,27 +7745,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FC+ub+4 [~5]</t>
+          <t>FC+ub+4</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FC+ub+4 [~5]</t>
+          <t>FC+ub+4</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FC+u+4 [~5]; FC+uf+4 [~5]</t>
+          <t>FC+u+4; FC+uf+4</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Quick Catapult [Tag]</t>
+          <t>Quick Catapult</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Quick Catapult [Tag]</t>
+          <t>Quick Catapult</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7714,10 +7800,15 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
           <t>f93c5bab-b4de-4025-ab8e-e8a4df68d102</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>191fe500-624f-4c55-b669-26ef7c6c80ea</t>
         </is>
@@ -7731,7 +7822,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FC+ub+4 [~5],3</t>
+          <t>FC+ub+4,3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7741,7 +7832,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Quick Catapult [Tag] – Twin Catapult</t>
+          <t>Quick Catapult – Twin Catapult</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7779,17 +7870,17 @@
           <t>Somersault will juggle on a hit if the previous kicks were blocked or whiffed.</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>66166acc-0611-4ca1-860e-c1073bb9d1e8</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>7bae2e2a-5e49-4d18-8b69-928133629252</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
+      <c r="AA84" t="inlineStr">
         <is>
           <t>f93c5bab-b4de-4025-ab8e-e8a4df68d102</t>
         </is>
@@ -7798,27 +7889,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FC+ub,4 [~5]</t>
+          <t>FC+ub,4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FC+ub,4 [~5]</t>
+          <t>FC+ub,4</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FC+u,4 [~5]; FC+uf,4 [~5]</t>
+          <t>FC+u,4; FC+uf,4</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Fake Somersault - Sky Kick [Tag]</t>
+          <t>Fake Somersault - Sky Kick</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Fake Somersault - Sky Kick [Tag]</t>
+          <t>Fake Somersault - Sky Kick</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7893,10 +7984,15 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
           <t>f8150537-d2b5-45f3-949b-b3203030cf7a</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>ab888ad0-6b2e-4796-a4d3-23c949e14959</t>
         </is>
@@ -7993,12 +8089,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="Y86" t="inlineStr">
         <is>
           <t>699629ac-1762-4d7a-bb0e-ee7fd7aa592d</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>957790c4-2003-45bc-b681-848868c400d9</t>
         </is>
@@ -8085,12 +8181,12 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
+      <c r="Y87" t="inlineStr">
         <is>
           <t>ad489638-4a04-4acd-8d31-d3bc98821fd8</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t>e146371d-6630-4de3-9e8c-3647a1aca9ef</t>
         </is>
@@ -8187,12 +8283,12 @@
           <t>hm</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
+      <c r="Y88" t="inlineStr">
         <is>
           <t>b2e82a93-31e9-43a7-aea2-3c4c0b68e5e8</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>8fb2c8e2-2e20-4789-84cf-ef882f41abf4</t>
         </is>
@@ -8294,12 +8390,12 @@
           <t>JG RC</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
+      <c r="Y89" t="inlineStr">
         <is>
           <t>d5470893-0664-44d9-b7fb-fc713f145d76</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t>9fa31d0b-0c2e-49d4-8377-07cb221512b2</t>
         </is>
@@ -8356,12 +8452,12 @@
           <t>JG RC</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>2423b71a-13d6-4e3d-a440-f4b48202f6a0</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>8496e70a-5e28-4dbc-b9d2-12087c07625a</t>
         </is>
@@ -8458,12 +8554,12 @@
           <t>JG RC</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
+      <c r="Y91" t="inlineStr">
         <is>
           <t>ca68cd01-1def-4191-a639-4d93dc57a076</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>a884d0dc-62b4-476b-b70d-efdca1272b25</t>
         </is>
@@ -8472,27 +8568,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>UB [~5]</t>
+          <t>UB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>UB [~5]</t>
+          <t>UB</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>U [~5]; UF+4 [~5]</t>
+          <t>U; UF+4</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Quick Advance Catapult [Tag]</t>
+          <t>Quick Advance Catapult</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Quick Advance Catapult [Tag]</t>
+          <t>Quick Advance Catapult</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -8567,10 +8663,15 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
           <t>5f803d22-cd2f-44cc-8aab-a48c0ef98f8f</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>cb625f7c-cea8-4829-a0d7-73c555b7c4f2</t>
         </is>
@@ -8584,7 +8685,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>UB [~5],3</t>
+          <t>UB,3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -8594,7 +8695,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Quick Advance Catapult [Tag] – Twin Catapult</t>
+          <t>Quick Advance Catapult – Twin Catapult</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8667,17 +8768,17 @@
           <t>Somersault will juggle on a hit if the previous kicks were blocked or whiffed.</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr">
+      <c r="Y93" t="inlineStr">
         <is>
           <t>35f76886-ee6d-4d1d-8478-16b3b2646e6d</t>
         </is>
       </c>
-      <c r="Y93" t="inlineStr">
+      <c r="Z93" t="inlineStr">
         <is>
           <t>72657d58-6cb9-4b55-b762-d975445770cf</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
+      <c r="AA93" t="inlineStr">
         <is>
           <t>5f803d22-cd2f-44cc-8aab-a48c0ef98f8f</t>
         </is>
@@ -8774,12 +8875,12 @@
           <t>MS</t>
         </is>
       </c>
-      <c r="X94" t="inlineStr">
+      <c r="Y94" t="inlineStr">
         <is>
           <t>b8f38937-2ac2-44d9-b316-ec006b6cc701</t>
         </is>
       </c>
-      <c r="Y94" t="inlineStr">
+      <c r="Z94" t="inlineStr">
         <is>
           <t>b6e18c00-4025-4dec-8e61-a482e922a24b</t>
         </is>
@@ -8836,12 +8937,12 @@
           <t>After a succesfull High or Mid Punch Parry.</t>
         </is>
       </c>
-      <c r="X95" t="inlineStr">
+      <c r="Y95" t="inlineStr">
         <is>
           <t>6d9d40ae-2a89-4741-a7bf-0814b416c893</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>0b98c9ca-4b26-4526-b3a5-e69dbaf5a56d</t>
         </is>
@@ -8918,17 +9019,17 @@
           <t>OB</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
+      <c r="Y96" t="inlineStr">
         <is>
           <t>151b36cf-1c89-4ebf-9ff4-80e9b329c4e7</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
+      <c r="Z96" t="inlineStr">
         <is>
           <t>79585969-5e1c-450f-b978-d558e427deaa</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
+      <c r="AA96" t="inlineStr">
         <is>
           <t>6d9d40ae-2a89-4741-a7bf-0814b416c893</t>
         </is>
@@ -9005,17 +9106,17 @@
           <t>SH</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
+      <c r="Y97" t="inlineStr">
         <is>
           <t>c2393db1-784e-4709-92af-5b72528fc505</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>bf4989b0-4e04-4451-9747-f8803fe166ac</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
+      <c r="AA97" t="inlineStr">
         <is>
           <t>6d9d40ae-2a89-4741-a7bf-0814b416c893</t>
         </is>
@@ -9087,17 +9188,17 @@
           <t>-h</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr">
+      <c r="Y98" t="inlineStr">
         <is>
           <t>71fa98e7-9568-4851-ab6c-7fd6c7e2d274</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>8610004c-3247-4a5d-89e6-d112faa80953</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
+      <c r="AA98" t="inlineStr">
         <is>
           <t>6d9d40ae-2a89-4741-a7bf-0814b416c893</t>
         </is>
@@ -9169,17 +9270,17 @@
           <t>-l</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
+      <c r="Y99" t="inlineStr">
         <is>
           <t>fabed8ed-5924-45e0-a411-784eb37ed5a7</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
           <t>1ad1b631-0b65-4a3f-a807-8d2b6bd08c73</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
+      <c r="AA99" t="inlineStr">
         <is>
           <t>6d9d40ae-2a89-4741-a7bf-0814b416c893</t>
         </is>
@@ -9236,12 +9337,12 @@
           <t>After a whiffed Punch Parry.</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="Y100" t="inlineStr">
         <is>
           <t>50e46797-fb0a-4bc1-9932-c48429c897e4</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>4a7293cd-8d74-43c1-ad30-f5124f5e79a5</t>
         </is>
@@ -9323,17 +9424,17 @@
           <t>-m</t>
         </is>
       </c>
-      <c r="X101" t="inlineStr">
+      <c r="Y101" t="inlineStr">
         <is>
           <t>6c7e61c3-42aa-414a-839a-264df4aac023</t>
         </is>
       </c>
-      <c r="Y101" t="inlineStr">
+      <c r="Z101" t="inlineStr">
         <is>
           <t>c52e87f4-1619-46db-8bf6-b18899ea9a31</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
+      <c r="AA101" t="inlineStr">
         <is>
           <t>50e46797-fb0a-4bc1-9932-c48429c897e4</t>
         </is>
@@ -9342,22 +9443,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>– 2 [~5]</t>
+          <t>– 2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>b+1+2,2 [~5]</t>
+          <t>b+1+2,2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>– Dragon Upper [Tag]</t>
+          <t>– Dragon Upper</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Tricky Step – Dragon Upper [Tag]</t>
+          <t>Tricky Step – Dragon Upper</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9422,15 +9523,20 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
           <t>24f9b7a8-0ebe-41a0-9ff5-e3cc82e6cade</t>
         </is>
       </c>
-      <c r="Y102" t="inlineStr">
+      <c r="Z102" t="inlineStr">
         <is>
           <t>bf859695-bf82-4b6b-adc3-f1b1e1564409</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
+      <c r="AA102" t="inlineStr">
         <is>
           <t>50e46797-fb0a-4bc1-9932-c48429c897e4</t>
         </is>
@@ -9512,17 +9618,17 @@
           <t>-l</t>
         </is>
       </c>
-      <c r="X103" t="inlineStr">
+      <c r="Y103" t="inlineStr">
         <is>
           <t>2098d992-dab9-4730-baef-adc3550f63a7</t>
         </is>
       </c>
-      <c r="Y103" t="inlineStr">
+      <c r="Z103" t="inlineStr">
         <is>
           <t>4729693c-9e9b-420b-93ba-0056127d8c7b</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
+      <c r="AA103" t="inlineStr">
         <is>
           <t>50e46797-fb0a-4bc1-9932-c48429c897e4</t>
         </is>
@@ -9614,12 +9720,12 @@
           <t>hl</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
+      <c r="Y104" t="inlineStr">
         <is>
           <t>4bc0bb16-c06a-40c6-92da-2c9e32de8780</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>ceb4e480-4fae-4339-97f9-eceb0bcd8c9f</t>
         </is>
@@ -9671,12 +9777,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X105" t="inlineStr">
+      <c r="Y105" t="inlineStr">
         <is>
           <t>b3ed089d-aea1-4337-adcc-505c4aa18798</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
+      <c r="Z105" t="inlineStr">
         <is>
           <t>bb4f2c24-14f2-4fd6-b549-c1cfe6465745</t>
         </is>
@@ -9733,12 +9839,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X106" t="inlineStr">
+      <c r="Y106" t="inlineStr">
         <is>
           <t>e723346f-757a-4380-befa-e17e9a7c2322</t>
         </is>
       </c>
-      <c r="Y106" t="inlineStr">
+      <c r="Z106" t="inlineStr">
         <is>
           <t>2db166c2-83fc-4ca9-82cc-c230e1efc7f2</t>
         </is>
@@ -9795,12 +9901,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X107" t="inlineStr">
+      <c r="Y107" t="inlineStr">
         <is>
           <t>69bd46de-18b6-458e-a176-b58215608db8</t>
         </is>
       </c>
-      <c r="Y107" t="inlineStr">
+      <c r="Z107" t="inlineStr">
         <is>
           <t>6d899d6c-8d70-4937-a6e1-3c4febb9bcee</t>
         </is>
@@ -9932,20 +10038,25 @@
       </c>
       <c r="X110" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y110" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y110" s="1" t="inlineStr">
+      <c r="Z110" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z110" s="1" t="inlineStr">
+      <c r="AA110" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA110" s="1" t="inlineStr">
+      <c r="AB110" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -10027,12 +10138,12 @@
           <t>!</t>
         </is>
       </c>
-      <c r="X111" t="inlineStr">
+      <c r="Y111" t="inlineStr">
         <is>
           <t>5a04a751-69b2-41d0-9389-f2af17c4c441</t>
         </is>
       </c>
-      <c r="Y111" t="inlineStr">
+      <c r="Z111" t="inlineStr">
         <is>
           <t>0b3f9cd1-212a-454c-bb18-8e1141a05aeb</t>
         </is>
@@ -10099,17 +10210,17 @@
           <t>!-</t>
         </is>
       </c>
-      <c r="X112" t="inlineStr">
+      <c r="Y112" t="inlineStr">
         <is>
           <t>df1fb304-3d0f-432a-a434-dcd6a830d220</t>
         </is>
       </c>
-      <c r="Y112" t="inlineStr">
+      <c r="Z112" t="inlineStr">
         <is>
           <t>3c47c2fb-baae-456b-85eb-b1baacf3478d</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
+      <c r="AA112" t="inlineStr">
         <is>
           <t>5a04a751-69b2-41d0-9389-f2af17c4c441</t>
         </is>
@@ -10241,20 +10352,25 @@
       </c>
       <c r="X115" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y115" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y115" s="1" t="inlineStr">
+      <c r="Z115" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z115" s="1" t="inlineStr">
+      <c r="AA115" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA115" s="1" t="inlineStr">
+      <c r="AB115" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -10296,12 +10412,12 @@
           <t>mhmhhLhhhm</t>
         </is>
       </c>
-      <c r="Y116" t="inlineStr">
+      <c r="Z116" t="inlineStr">
         <is>
           <t>3176b347-df34-4e1d-aba7-0986acc47022</t>
         </is>
       </c>
-      <c r="AA116" t="inlineStr">
+      <c r="AB116" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -10343,12 +10459,12 @@
           <t>mhmhhLmlLm</t>
         </is>
       </c>
-      <c r="Y117" t="inlineStr">
+      <c r="Z117" t="inlineStr">
         <is>
           <t>f1b78286-7ba8-4bda-bee5-c8b848d48f48</t>
         </is>
       </c>
-      <c r="AA117" t="inlineStr">
+      <c r="AB117" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -10390,12 +10506,12 @@
           <t>mhmhhLmlLm</t>
         </is>
       </c>
-      <c r="Y118" t="inlineStr">
+      <c r="Z118" t="inlineStr">
         <is>
           <t>58c32a2c-b1e2-4611-949c-911167465bf7</t>
         </is>
       </c>
-      <c r="AA118" t="inlineStr">
+      <c r="AB118" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -10437,12 +10553,12 @@
           <t>mlmhhLhhhm</t>
         </is>
       </c>
-      <c r="Y119" t="inlineStr">
+      <c r="Z119" t="inlineStr">
         <is>
           <t>30f18387-0cd0-40f9-bf5b-9602c4d57833</t>
         </is>
       </c>
-      <c r="AA119" t="inlineStr">
+      <c r="AB119" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -10484,12 +10600,12 @@
           <t>mlmhhLmhlm</t>
         </is>
       </c>
-      <c r="Y120" t="inlineStr">
+      <c r="Z120" t="inlineStr">
         <is>
           <t>a1dab966-d331-415b-9775-354f1c4d19a5</t>
         </is>
       </c>
-      <c r="AA120" t="inlineStr">
+      <c r="AB120" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -10531,12 +10647,12 @@
           <t>mlmhhLmlLm</t>
         </is>
       </c>
-      <c r="Y121" t="inlineStr">
+      <c r="Z121" t="inlineStr">
         <is>
           <t>99593a10-9a71-4270-8908-8fdf661c902a</t>
         </is>
       </c>
-      <c r="AA121" t="inlineStr">
+      <c r="AB121" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/forest_step7.xlsx
+++ b/sources/forest_step7.xlsx
@@ -4966,22 +4966,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>– ~4 [~D]</t>
+          <t>– ~4</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>db+2~4 [~D]</t>
+          <t>db+2~4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>– Spring Kick [PLD]</t>
+          <t>– Spring Kick</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dragon Whip – Spring Kick [PLD]</t>
+          <t>Dragon Whip – Spring Kick</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>(~D)PLD</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -7337,22 +7342,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>d+3+4 [~D]</t>
+          <t>d+3+4</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>d+3+4 [~D]</t>
+          <t>d+3+4</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Frog Man [KND]</t>
+          <t>Frog Man</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Frog Man [KND]</t>
+          <t>Frog Man</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>(~D)KND</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">

--- a/sources/forest_step7.xlsx
+++ b/sources/forest_step7.xlsx
@@ -990,6 +990,11 @@
           <t>The initial grab does no damage.</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>c496aa41-bc15-473a-b020-7fdb437577cf</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>c496aa41-bc15-473a-b020-7fdb437577cf</t>
@@ -1057,6 +1062,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>daf033ef-4b67-4b29-86af-e6b2fab70477</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>daf033ef-4b67-4b29-86af-e6b2fab70477</t>
@@ -1119,6 +1129,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1726e35f-9e18-4c65-a787-332f9f98cc84</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>1726e35f-9e18-4c65-a787-332f9f98cc84</t>
@@ -1179,6 +1194,11 @@
       <c r="U11" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>a1c6311d-6e89-4a3a-b759-44f0ce100eea</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -10422,6 +10442,11 @@
           <t>mhmhhLhhhm</t>
         </is>
       </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>3176b347-df34-4e1d-aba7-0986acc47022</t>
+        </is>
+      </c>
       <c r="Z116" t="inlineStr">
         <is>
           <t>3176b347-df34-4e1d-aba7-0986acc47022</t>
@@ -10469,6 +10494,11 @@
           <t>mhmhhLmlLm</t>
         </is>
       </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>f1b78286-7ba8-4bda-bee5-c8b848d48f48</t>
+        </is>
+      </c>
       <c r="Z117" t="inlineStr">
         <is>
           <t>f1b78286-7ba8-4bda-bee5-c8b848d48f48</t>
@@ -10516,6 +10546,11 @@
           <t>mhmhhLmlLm</t>
         </is>
       </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>58c32a2c-b1e2-4611-949c-911167465bf7</t>
+        </is>
+      </c>
       <c r="Z118" t="inlineStr">
         <is>
           <t>58c32a2c-b1e2-4611-949c-911167465bf7</t>
@@ -10563,6 +10598,11 @@
           <t>mlmhhLhhhm</t>
         </is>
       </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>30f18387-0cd0-40f9-bf5b-9602c4d57833</t>
+        </is>
+      </c>
       <c r="Z119" t="inlineStr">
         <is>
           <t>30f18387-0cd0-40f9-bf5b-9602c4d57833</t>
@@ -10610,6 +10650,11 @@
           <t>mlmhhLmhlm</t>
         </is>
       </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>a1dab966-d331-415b-9775-354f1c4d19a5</t>
+        </is>
+      </c>
       <c r="Z120" t="inlineStr">
         <is>
           <t>a1dab966-d331-415b-9775-354f1c4d19a5</t>
@@ -10655,6 +10700,11 @@
       <c r="S121" t="inlineStr">
         <is>
           <t>mlmhhLmlLm</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>99593a10-9a71-4270-8908-8fdf661c902a</t>
         </is>
       </c>
       <c r="Z121" t="inlineStr">
